--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>121232821</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232808</v>
+        <v>121232817</v>
       </c>
       <c r="B5" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577061</v>
+        <v>577099</v>
       </c>
       <c r="R5" t="n">
-        <v>7188065</v>
+        <v>7188163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232811</v>
+        <v>121232803</v>
       </c>
       <c r="B6" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577105</v>
+        <v>576964</v>
       </c>
       <c r="R6" t="n">
-        <v>7188120</v>
+        <v>7188008</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232863</v>
+        <v>121232819</v>
       </c>
       <c r="B7" t="n">
-        <v>90687</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,34 +1238,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576931</v>
+        <v>577007</v>
       </c>
       <c r="R7" t="n">
-        <v>7188099</v>
+        <v>7188162</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232801</v>
+        <v>121232863</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
+        <v>90697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,39 +1345,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576960</v>
+        <v>576931</v>
       </c>
       <c r="R8" t="n">
-        <v>7188040</v>
+        <v>7188099</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
         <v>121232805</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>121232862</v>
       </c>
       <c r="B10" t="n">
-        <v>91370</v>
+        <v>91380</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232799</v>
+        <v>121232801</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576936</v>
+        <v>576960</v>
       </c>
       <c r="R11" t="n">
-        <v>7188098</v>
+        <v>7188040</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232803</v>
+        <v>121232799</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576964</v>
+        <v>576936</v>
       </c>
       <c r="R12" t="n">
-        <v>7188008</v>
+        <v>7188098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232817</v>
+        <v>121232813</v>
       </c>
       <c r="B13" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577099</v>
+        <v>577263</v>
       </c>
       <c r="R13" t="n">
-        <v>7188163</v>
+        <v>7188315</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232819</v>
+        <v>121232808</v>
       </c>
       <c r="B14" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577007</v>
+        <v>577061</v>
       </c>
       <c r="R14" t="n">
-        <v>7188162</v>
+        <v>7188065</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232813</v>
+        <v>121232811</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577263</v>
+        <v>577105</v>
       </c>
       <c r="R15" t="n">
-        <v>7188315</v>
+        <v>7188120</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232821</v>
+        <v>121232801</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576992</v>
+        <v>576960</v>
       </c>
       <c r="R4" t="n">
-        <v>7188167</v>
+        <v>7188040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232817</v>
+        <v>121232862</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>91380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,43 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577099</v>
+        <v>576944</v>
       </c>
       <c r="R5" t="n">
-        <v>7188163</v>
+        <v>7187952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232803</v>
+        <v>121232808</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1160,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576964</v>
+        <v>577061</v>
       </c>
       <c r="R6" t="n">
-        <v>7188008</v>
+        <v>7188065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1217,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232819</v>
+        <v>121232799</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1267,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577007</v>
+        <v>576936</v>
       </c>
       <c r="R7" t="n">
-        <v>7188162</v>
+        <v>7188098</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232863</v>
+        <v>121232817</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,34 +1340,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576931</v>
+        <v>577099</v>
       </c>
       <c r="R8" t="n">
-        <v>7188099</v>
+        <v>7188163</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1431,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232805</v>
+        <v>121232819</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576977</v>
+        <v>577007</v>
       </c>
       <c r="R9" t="n">
-        <v>7187989</v>
+        <v>7188162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232862</v>
+        <v>121232821</v>
       </c>
       <c r="B10" t="n">
-        <v>91380</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,38 +1550,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576944</v>
+        <v>576992</v>
       </c>
       <c r="R10" t="n">
-        <v>7187952</v>
+        <v>7188167</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232801</v>
+        <v>121232811</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1685,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576960</v>
+        <v>577105</v>
       </c>
       <c r="R11" t="n">
-        <v>7188040</v>
+        <v>7188120</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232799</v>
+        <v>121232863</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1763,39 +1768,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576936</v>
+        <v>576931</v>
       </c>
       <c r="R12" t="n">
-        <v>7188098</v>
+        <v>7188099</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232808</v>
+        <v>121232803</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577061</v>
+        <v>576964</v>
       </c>
       <c r="R14" t="n">
-        <v>7188065</v>
+        <v>7188008</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232811</v>
+        <v>121232805</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577105</v>
+        <v>576977</v>
       </c>
       <c r="R15" t="n">
-        <v>7188120</v>
+        <v>7187989</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232801</v>
+        <v>121232803</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576960</v>
+        <v>576964</v>
       </c>
       <c r="R4" t="n">
-        <v>7188040</v>
+        <v>7188008</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232862</v>
+        <v>121232817</v>
       </c>
       <c r="B5" t="n">
-        <v>91380</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1020,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576944</v>
+        <v>577099</v>
       </c>
       <c r="R5" t="n">
-        <v>7187952</v>
+        <v>7188163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232808</v>
+        <v>121232821</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1155,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577061</v>
+        <v>576992</v>
       </c>
       <c r="R6" t="n">
-        <v>7188065</v>
+        <v>7188167</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232799</v>
+        <v>121232862</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>91392</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,43 +1234,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576936</v>
+        <v>576944</v>
       </c>
       <c r="R7" t="n">
-        <v>7188098</v>
+        <v>7187952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232817</v>
+        <v>121232808</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577099</v>
+        <v>577061</v>
       </c>
       <c r="R8" t="n">
-        <v>7188163</v>
+        <v>7188065</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232819</v>
+        <v>121232863</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>90709</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,39 +1447,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577007</v>
+        <v>576931</v>
       </c>
       <c r="R9" t="n">
-        <v>7188162</v>
+        <v>7188099</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232821</v>
+        <v>121232811</v>
       </c>
       <c r="B10" t="n">
         <v>57351</v>
@@ -1583,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576992</v>
+        <v>577105</v>
       </c>
       <c r="R10" t="n">
-        <v>7188167</v>
+        <v>7188120</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,7 +1640,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232811</v>
+        <v>121232799</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1690,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577105</v>
+        <v>576936</v>
       </c>
       <c r="R11" t="n">
-        <v>7188120</v>
+        <v>7188098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232863</v>
+        <v>121232801</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,34 +1763,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576931</v>
+        <v>576960</v>
       </c>
       <c r="R12" t="n">
-        <v>7188099</v>
+        <v>7188040</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232813</v>
+        <v>121232819</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577263</v>
+        <v>577007</v>
       </c>
       <c r="R13" t="n">
-        <v>7188315</v>
+        <v>7188162</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232803</v>
+        <v>121232805</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576964</v>
+        <v>576977</v>
       </c>
       <c r="R14" t="n">
-        <v>7188008</v>
+        <v>7187989</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232805</v>
+        <v>121232813</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576977</v>
+        <v>577263</v>
       </c>
       <c r="R15" t="n">
-        <v>7187989</v>
+        <v>7188315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232803</v>
+        <v>121232817</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576964</v>
+        <v>577099</v>
       </c>
       <c r="R4" t="n">
-        <v>7188008</v>
+        <v>7188163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232817</v>
+        <v>121232799</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577099</v>
+        <v>576936</v>
       </c>
       <c r="R5" t="n">
-        <v>7188163</v>
+        <v>7188098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232821</v>
+        <v>121232863</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>90710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,39 +1131,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576992</v>
+        <v>576931</v>
       </c>
       <c r="R6" t="n">
-        <v>7188167</v>
+        <v>7188099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1220,7 @@
         <v>121232862</v>
       </c>
       <c r="B7" t="n">
-        <v>91392</v>
+        <v>91393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1324,7 +1319,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232808</v>
+        <v>121232805</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1369,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577061</v>
+        <v>576977</v>
       </c>
       <c r="R8" t="n">
-        <v>7188065</v>
+        <v>7187989</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232863</v>
+        <v>121232801</v>
       </c>
       <c r="B9" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,34 +1442,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576931</v>
+        <v>576960</v>
       </c>
       <c r="R9" t="n">
-        <v>7188099</v>
+        <v>7188040</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232811</v>
+        <v>121232813</v>
       </c>
       <c r="B10" t="n">
         <v>57351</v>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577105</v>
+        <v>577263</v>
       </c>
       <c r="R10" t="n">
-        <v>7188120</v>
+        <v>7188315</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,7 +1640,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232799</v>
+        <v>121232808</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576936</v>
+        <v>577061</v>
       </c>
       <c r="R11" t="n">
-        <v>7188098</v>
+        <v>7188065</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232801</v>
+        <v>121232821</v>
       </c>
       <c r="B12" t="n">
         <v>57351</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576960</v>
+        <v>576992</v>
       </c>
       <c r="R12" t="n">
-        <v>7188040</v>
+        <v>7188167</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232819</v>
+        <v>121232803</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577007</v>
+        <v>576964</v>
       </c>
       <c r="R13" t="n">
-        <v>7188162</v>
+        <v>7188008</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232805</v>
+        <v>121232819</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576977</v>
+        <v>577007</v>
       </c>
       <c r="R14" t="n">
-        <v>7187989</v>
+        <v>7188162</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232813</v>
+        <v>121232811</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577263</v>
+        <v>577105</v>
       </c>
       <c r="R15" t="n">
-        <v>7188315</v>
+        <v>7188120</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232817</v>
+        <v>121232803</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577099</v>
+        <v>576964</v>
       </c>
       <c r="R4" t="n">
-        <v>7188163</v>
+        <v>7188008</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232799</v>
+        <v>121232808</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576936</v>
+        <v>577061</v>
       </c>
       <c r="R5" t="n">
-        <v>7188098</v>
+        <v>7188065</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1118,7 @@
         <v>121232863</v>
       </c>
       <c r="B6" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232862</v>
+        <v>121232813</v>
       </c>
       <c r="B7" t="n">
-        <v>91393</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,38 +1229,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576944</v>
+        <v>577263</v>
       </c>
       <c r="R7" t="n">
-        <v>7187952</v>
+        <v>7188315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232805</v>
+        <v>121232811</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576977</v>
+        <v>577105</v>
       </c>
       <c r="R8" t="n">
-        <v>7187989</v>
+        <v>7188120</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1434,7 @@
         <v>121232801</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232813</v>
+        <v>121232799</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577263</v>
+        <v>576936</v>
       </c>
       <c r="R10" t="n">
-        <v>7188315</v>
+        <v>7188098</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232808</v>
+        <v>121232805</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577061</v>
+        <v>576977</v>
       </c>
       <c r="R11" t="n">
-        <v>7188065</v>
+        <v>7187989</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232821</v>
+        <v>121232819</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576992</v>
+        <v>577007</v>
       </c>
       <c r="R12" t="n">
-        <v>7188167</v>
+        <v>7188162</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232803</v>
+        <v>121232821</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576964</v>
+        <v>576992</v>
       </c>
       <c r="R13" t="n">
-        <v>7188008</v>
+        <v>7188167</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,10 +1966,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232819</v>
+        <v>121232817</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577007</v>
+        <v>577099</v>
       </c>
       <c r="R14" t="n">
-        <v>7188162</v>
+        <v>7188163</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232811</v>
+        <v>121232862</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>91396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,43 +2085,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577105</v>
+        <v>576944</v>
       </c>
       <c r="R15" t="n">
-        <v>7188120</v>
+        <v>7187952</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232803</v>
+        <v>121232862</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>91396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,43 +913,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576964</v>
+        <v>576944</v>
       </c>
       <c r="R4" t="n">
-        <v>7188008</v>
+        <v>7187952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232808</v>
+        <v>121232805</v>
       </c>
       <c r="B5" t="n">
         <v>57354</v>
@@ -1053,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577061</v>
+        <v>576977</v>
       </c>
       <c r="R5" t="n">
-        <v>7188065</v>
+        <v>7187989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232863</v>
+        <v>121232813</v>
       </c>
       <c r="B6" t="n">
-        <v>90713</v>
+        <v>57354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,34 +1126,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576931</v>
+        <v>577263</v>
       </c>
       <c r="R6" t="n">
-        <v>7188099</v>
+        <v>7188315</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232813</v>
+        <v>121232801</v>
       </c>
       <c r="B7" t="n">
         <v>57354</v>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577263</v>
+        <v>576960</v>
       </c>
       <c r="R7" t="n">
-        <v>7188315</v>
+        <v>7188040</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232811</v>
+        <v>121232863</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>90713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,39 +1340,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577105</v>
+        <v>576931</v>
       </c>
       <c r="R8" t="n">
-        <v>7188120</v>
+        <v>7188099</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1426,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232801</v>
+        <v>121232799</v>
       </c>
       <c r="B9" t="n">
         <v>57354</v>
@@ -1476,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576960</v>
+        <v>576936</v>
       </c>
       <c r="R9" t="n">
-        <v>7188040</v>
+        <v>7188098</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232799</v>
+        <v>121232811</v>
       </c>
       <c r="B10" t="n">
         <v>57354</v>
@@ -1583,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576936</v>
+        <v>577105</v>
       </c>
       <c r="R10" t="n">
-        <v>7188098</v>
+        <v>7188120</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,7 +1640,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232805</v>
+        <v>121232821</v>
       </c>
       <c r="B11" t="n">
         <v>57354</v>
@@ -1690,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576977</v>
+        <v>576992</v>
       </c>
       <c r="R11" t="n">
-        <v>7187989</v>
+        <v>7188167</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1859,7 +1854,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232821</v>
+        <v>121232808</v>
       </c>
       <c r="B13" t="n">
         <v>57354</v>
@@ -1904,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576992</v>
+        <v>577061</v>
       </c>
       <c r="R13" t="n">
-        <v>7188167</v>
+        <v>7188065</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1961,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232817</v>
+        <v>121232803</v>
       </c>
       <c r="B14" t="n">
         <v>57354</v>
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577099</v>
+        <v>576964</v>
       </c>
       <c r="R14" t="n">
-        <v>7188163</v>
+        <v>7188008</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232862</v>
+        <v>121232817</v>
       </c>
       <c r="B15" t="n">
-        <v>91396</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,38 +2080,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576944</v>
+        <v>577099</v>
       </c>
       <c r="R15" t="n">
-        <v>7187952</v>
+        <v>7188163</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232863</v>
+        <v>121232799</v>
       </c>
       <c r="B8" t="n">
-        <v>90713</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,34 +1340,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576931</v>
+        <v>576936</v>
       </c>
       <c r="R8" t="n">
-        <v>7188099</v>
+        <v>7188098</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232799</v>
+        <v>121232863</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>90713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,39 +1447,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576936</v>
+        <v>576931</v>
       </c>
       <c r="R9" t="n">
-        <v>7188098</v>
+        <v>7188099</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232862</v>
+        <v>121232819</v>
       </c>
       <c r="B4" t="n">
-        <v>91396</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,38 +913,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576944</v>
+        <v>577007</v>
       </c>
       <c r="R4" t="n">
-        <v>7187952</v>
+        <v>7188162</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232805</v>
+        <v>121232862</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>91402</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,43 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576977</v>
+        <v>576944</v>
       </c>
       <c r="R5" t="n">
-        <v>7187989</v>
+        <v>7187952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232813</v>
+        <v>121232805</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577263</v>
+        <v>576977</v>
       </c>
       <c r="R6" t="n">
-        <v>7188315</v>
+        <v>7187989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232801</v>
+        <v>121232811</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576960</v>
+        <v>577105</v>
       </c>
       <c r="R7" t="n">
-        <v>7188040</v>
+        <v>7188120</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232799</v>
+        <v>121232803</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576936</v>
+        <v>576964</v>
       </c>
       <c r="R8" t="n">
-        <v>7188098</v>
+        <v>7188008</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232863</v>
+        <v>121232821</v>
       </c>
       <c r="B9" t="n">
-        <v>90713</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,34 +1447,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576931</v>
+        <v>576992</v>
       </c>
       <c r="R9" t="n">
-        <v>7188099</v>
+        <v>7188167</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232811</v>
+        <v>121232799</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577105</v>
+        <v>576936</v>
       </c>
       <c r="R10" t="n">
-        <v>7188120</v>
+        <v>7188098</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232821</v>
+        <v>121232808</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576992</v>
+        <v>577061</v>
       </c>
       <c r="R11" t="n">
-        <v>7188167</v>
+        <v>7188065</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232819</v>
+        <v>121232813</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577007</v>
+        <v>577263</v>
       </c>
       <c r="R12" t="n">
-        <v>7188162</v>
+        <v>7188315</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232808</v>
+        <v>121232817</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577061</v>
+        <v>577099</v>
       </c>
       <c r="R13" t="n">
-        <v>7188065</v>
+        <v>7188163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,10 +1966,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232803</v>
+        <v>121232863</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>90719</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,39 +1982,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576964</v>
+        <v>576931</v>
       </c>
       <c r="R14" t="n">
-        <v>7188008</v>
+        <v>7188099</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232817</v>
+        <v>121232801</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577099</v>
+        <v>576960</v>
       </c>
       <c r="R15" t="n">
-        <v>7188163</v>
+        <v>7188040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232819</v>
+        <v>121232811</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577007</v>
+        <v>577105</v>
       </c>
       <c r="R4" t="n">
-        <v>7188162</v>
+        <v>7188120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232862</v>
+        <v>121232821</v>
       </c>
       <c r="B5" t="n">
-        <v>91402</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1020,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576944</v>
+        <v>576992</v>
       </c>
       <c r="R5" t="n">
-        <v>7187952</v>
+        <v>7188167</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232805</v>
+        <v>121232862</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>91403</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,43 +1127,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576977</v>
+        <v>576944</v>
       </c>
       <c r="R6" t="n">
-        <v>7187989</v>
+        <v>7187952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232811</v>
+        <v>121232801</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577105</v>
+        <v>576960</v>
       </c>
       <c r="R7" t="n">
-        <v>7188120</v>
+        <v>7188040</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232803</v>
+        <v>121232817</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576964</v>
+        <v>577099</v>
       </c>
       <c r="R8" t="n">
-        <v>7188008</v>
+        <v>7188163</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232821</v>
+        <v>121232863</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,39 +1447,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576992</v>
+        <v>576931</v>
       </c>
       <c r="R9" t="n">
-        <v>7188167</v>
+        <v>7188099</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232799</v>
+        <v>121232803</v>
       </c>
       <c r="B10" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576936</v>
+        <v>576964</v>
       </c>
       <c r="R10" t="n">
-        <v>7188098</v>
+        <v>7188008</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232808</v>
+        <v>121232819</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577061</v>
+        <v>577007</v>
       </c>
       <c r="R11" t="n">
-        <v>7188065</v>
+        <v>7188162</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232813</v>
+        <v>121232799</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577263</v>
+        <v>576936</v>
       </c>
       <c r="R12" t="n">
-        <v>7188315</v>
+        <v>7188098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232817</v>
+        <v>121232813</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577099</v>
+        <v>577263</v>
       </c>
       <c r="R13" t="n">
-        <v>7188163</v>
+        <v>7188315</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232863</v>
+        <v>121232805</v>
       </c>
       <c r="B14" t="n">
-        <v>90719</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,34 +1977,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576931</v>
+        <v>576977</v>
       </c>
       <c r="R14" t="n">
-        <v>7188099</v>
+        <v>7187989</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232801</v>
+        <v>121232808</v>
       </c>
       <c r="B15" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576960</v>
+        <v>577061</v>
       </c>
       <c r="R15" t="n">
-        <v>7188040</v>
+        <v>7188065</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232811</v>
+        <v>121232805</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577105</v>
+        <v>576977</v>
       </c>
       <c r="R4" t="n">
-        <v>7188120</v>
+        <v>7187989</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232821</v>
+        <v>121232808</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576992</v>
+        <v>577061</v>
       </c>
       <c r="R5" t="n">
-        <v>7188167</v>
+        <v>7188065</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232862</v>
+        <v>121232821</v>
       </c>
       <c r="B6" t="n">
-        <v>91403</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,38 +1127,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576944</v>
+        <v>576992</v>
       </c>
       <c r="R6" t="n">
-        <v>7187952</v>
+        <v>7188167</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232801</v>
+        <v>121232799</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1262,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576960</v>
+        <v>576936</v>
       </c>
       <c r="R7" t="n">
-        <v>7188040</v>
+        <v>7188098</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1329,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232817</v>
+        <v>121232803</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1369,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577099</v>
+        <v>576964</v>
       </c>
       <c r="R8" t="n">
-        <v>7188163</v>
+        <v>7188008</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232863</v>
+        <v>121232813</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,34 +1452,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576931</v>
+        <v>577263</v>
       </c>
       <c r="R9" t="n">
-        <v>7188099</v>
+        <v>7188315</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232803</v>
+        <v>121232863</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,39 +1559,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576964</v>
+        <v>576931</v>
       </c>
       <c r="R10" t="n">
-        <v>7188008</v>
+        <v>7188099</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232819</v>
+        <v>121232801</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1685,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577007</v>
+        <v>576960</v>
       </c>
       <c r="R11" t="n">
-        <v>7188162</v>
+        <v>7188040</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1752,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232799</v>
+        <v>121232817</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1792,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576936</v>
+        <v>577099</v>
       </c>
       <c r="R12" t="n">
-        <v>7188098</v>
+        <v>7188163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232813</v>
+        <v>121232862</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>91403</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,43 +1871,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577263</v>
+        <v>576944</v>
       </c>
       <c r="R13" t="n">
-        <v>7188315</v>
+        <v>7187952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232805</v>
+        <v>121232819</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576977</v>
+        <v>577007</v>
       </c>
       <c r="R14" t="n">
-        <v>7187989</v>
+        <v>7188162</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232808</v>
+        <v>121232811</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577061</v>
+        <v>577105</v>
       </c>
       <c r="R15" t="n">
-        <v>7188065</v>
+        <v>7188120</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232805</v>
+        <v>121232803</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576977</v>
+        <v>576964</v>
       </c>
       <c r="R4" t="n">
-        <v>7187989</v>
+        <v>7188008</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232808</v>
+        <v>121232801</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577061</v>
+        <v>576960</v>
       </c>
       <c r="R5" t="n">
-        <v>7188065</v>
+        <v>7188040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232821</v>
+        <v>121232808</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576992</v>
+        <v>577061</v>
       </c>
       <c r="R6" t="n">
-        <v>7188167</v>
+        <v>7188065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232799</v>
+        <v>121232821</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576936</v>
+        <v>576992</v>
       </c>
       <c r="R7" t="n">
-        <v>7188098</v>
+        <v>7188167</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232803</v>
+        <v>121232862</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>91403</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,43 +1341,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576964</v>
+        <v>576944</v>
       </c>
       <c r="R8" t="n">
-        <v>7188008</v>
+        <v>7187952</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1543,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232863</v>
+        <v>121232819</v>
       </c>
       <c r="B10" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,34 +1554,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576931</v>
+        <v>577007</v>
       </c>
       <c r="R10" t="n">
-        <v>7188099</v>
+        <v>7188162</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232801</v>
+        <v>121232863</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,39 +1661,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576960</v>
+        <v>576931</v>
       </c>
       <c r="R11" t="n">
-        <v>7188040</v>
+        <v>7188099</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1859,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232862</v>
+        <v>121232811</v>
       </c>
       <c r="B13" t="n">
-        <v>91403</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1871,38 +1866,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576944</v>
+        <v>577105</v>
       </c>
       <c r="R13" t="n">
-        <v>7187952</v>
+        <v>7188120</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232819</v>
+        <v>121232805</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577007</v>
+        <v>576977</v>
       </c>
       <c r="R14" t="n">
-        <v>7188162</v>
+        <v>7187989</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232811</v>
+        <v>121232799</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577105</v>
+        <v>576936</v>
       </c>
       <c r="R15" t="n">
-        <v>7188120</v>
+        <v>7188098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232803</v>
+        <v>121232801</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576964</v>
+        <v>576960</v>
       </c>
       <c r="R4" t="n">
-        <v>7188008</v>
+        <v>7188040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232801</v>
+        <v>121232817</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576960</v>
+        <v>577099</v>
       </c>
       <c r="R5" t="n">
-        <v>7188040</v>
+        <v>7188163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232808</v>
+        <v>121232819</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577061</v>
+        <v>577007</v>
       </c>
       <c r="R6" t="n">
-        <v>7188065</v>
+        <v>7188162</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232821</v>
+        <v>121232813</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576992</v>
+        <v>577263</v>
       </c>
       <c r="R7" t="n">
-        <v>7188167</v>
+        <v>7188315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232862</v>
+        <v>121232811</v>
       </c>
       <c r="B8" t="n">
-        <v>91403</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,38 +1341,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576944</v>
+        <v>577105</v>
       </c>
       <c r="R8" t="n">
-        <v>7187952</v>
+        <v>7188120</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1436,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232813</v>
+        <v>121232808</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1476,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577263</v>
+        <v>577061</v>
       </c>
       <c r="R9" t="n">
-        <v>7188315</v>
+        <v>7188065</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1543,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232819</v>
+        <v>121232803</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1583,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577007</v>
+        <v>576964</v>
       </c>
       <c r="R10" t="n">
-        <v>7188162</v>
+        <v>7188008</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232863</v>
+        <v>121232799</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,34 +1666,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576931</v>
+        <v>576936</v>
       </c>
       <c r="R11" t="n">
-        <v>7188099</v>
+        <v>7188098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1757,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232817</v>
+        <v>121232805</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1792,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577099</v>
+        <v>576977</v>
       </c>
       <c r="R12" t="n">
-        <v>7188163</v>
+        <v>7187989</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232811</v>
+        <v>121232862</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>91403</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,43 +1876,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577105</v>
+        <v>576944</v>
       </c>
       <c r="R13" t="n">
-        <v>7188120</v>
+        <v>7187952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,7 +1966,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232805</v>
+        <v>121232821</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576977</v>
+        <v>576992</v>
       </c>
       <c r="R14" t="n">
-        <v>7187989</v>
+        <v>7188167</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232799</v>
+        <v>121232863</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2084,39 +2089,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576936</v>
+        <v>576931</v>
       </c>
       <c r="R15" t="n">
-        <v>7188098</v>
+        <v>7188099</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104004571</v>
+        <v>121232863</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,20 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576931.9821213607</v>
+        <v>576931</v>
       </c>
       <c r="R2" t="n">
-        <v>7188099.179886523</v>
+        <v>7188099</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104004733</v>
+        <v>121232862</v>
       </c>
       <c r="B3" t="n">
-        <v>90074</v>
+        <v>91403</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,20 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576944.7012200544</v>
+        <v>576944</v>
       </c>
       <c r="R3" t="n">
-        <v>7187952.429859701</v>
+        <v>7187952</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1864,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232862</v>
+        <v>121232821</v>
       </c>
       <c r="B13" t="n">
-        <v>91403</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1876,38 +1854,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576944</v>
+        <v>576992</v>
       </c>
       <c r="R13" t="n">
-        <v>7187952</v>
+        <v>7188167</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,215 +1946,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>121232821</v>
-      </c>
-      <c r="B14" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>576992</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7188167</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>121232863</v>
-      </c>
-      <c r="B15" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>576931</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7188099</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38534-2024 artfynd.xlsx
+++ b/artfynd/A 38534-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>121232863</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121232862</v>
+        <v>121232866</v>
       </c>
       <c r="B3" t="n">
-        <v>91403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>2813</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576944</v>
+        <v>576880</v>
       </c>
       <c r="R3" t="n">
-        <v>7187952</v>
+        <v>7188090</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,55 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232801</v>
+        <v>121232862</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576960</v>
+        <v>576944</v>
       </c>
       <c r="R4" t="n">
-        <v>7188040</v>
+        <v>7187952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121232817</v>
+        <v>121232799</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577099</v>
+        <v>576936</v>
       </c>
       <c r="R5" t="n">
-        <v>7188163</v>
+        <v>7188098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121232819</v>
+        <v>121232801</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577007</v>
+        <v>576960</v>
       </c>
       <c r="R6" t="n">
-        <v>7188162</v>
+        <v>7188040</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121232813</v>
+        <v>121232803</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577263</v>
+        <v>576964</v>
       </c>
       <c r="R7" t="n">
-        <v>7188315</v>
+        <v>7188008</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,15 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232811</v>
+        <v>121232805</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577105</v>
+        <v>576977</v>
       </c>
       <c r="R8" t="n">
-        <v>7188120</v>
+        <v>7187989</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,12 +1377,7 @@
         <v>121232808</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,15 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232803</v>
+        <v>121232811</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576964</v>
+        <v>577105</v>
       </c>
       <c r="R10" t="n">
-        <v>7188008</v>
+        <v>7188120</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,15 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232799</v>
+        <v>121232813</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576936</v>
+        <v>577263</v>
       </c>
       <c r="R11" t="n">
-        <v>7188098</v>
+        <v>7188315</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,15 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232805</v>
+        <v>121232815</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576977</v>
+        <v>577281</v>
       </c>
       <c r="R12" t="n">
-        <v>7187989</v>
+        <v>7188328</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,15 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232821</v>
+        <v>121232817</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576992</v>
+        <v>577099</v>
       </c>
       <c r="R13" t="n">
-        <v>7188167</v>
+        <v>7188163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,6 +1881,516 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121232819</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björnberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577007</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7188162</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121232821</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Björnberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>576992</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7188167</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121232823</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Björnberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>576901</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7188159</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121232834</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Björnberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>576888</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7187894</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121232868</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Björnberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>576879</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7188076</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
